--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_otherspine[Mod道具信息-OtherSpine].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_otherspine[Mod道具信息-OtherSpine].xlsx
@@ -112,7 +112,7 @@
     <t>道具来源(逗号分隔枚举值,空=默认来源) 1=征服模式奖励</t>
   </si>
   <si>
-    <t>Item_TransformPotion_1</t>
+    <t>Item_Potion_1</t>
   </si>
   <si>
     <t>show_res:Amelia_SkeletonData&amp;ui_show_res:Amelia_Avator_SkeletonData&amp;ui_show_data:0.1164;-1,-226&amp;show_data:0.9086;1,-69&amp;world_data:0.5849;0,0</t>
@@ -250,7 +250,7 @@
     <t>Other幻化药(Eleamor/Eleamor)</t>
   </si>
   <si>
-    <t>show_res:Emma_SkeletonData&amp;ui_show_res:Emma_Avator_SkeletonData&amp;ui_show_data:0.1152;-9,-216&amp;show_data:1.1237;1,-80&amp;world_data:0.5305;0,0</t>
+    <t>show_res:Emma_SkeletonData&amp;ui_show_res:Emma_Avator_SkeletonData&amp;ui_show_data:0.1152;-9,-216&amp;show_data:1.0702;1,-80&amp;world_data:0.5305;0,0</t>
   </si>
   <si>
     <t>Other幻化药(Emma/Emma)</t>
